--- a/artfynd/A 5904-2024 artfynd.xlsx
+++ b/artfynd/A 5904-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5904-2024 artfynd.xlsx
+++ b/artfynd/A 5904-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94594241</v>
+        <v>94594321</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718700.9729891398</v>
+        <v>718746</v>
       </c>
       <c r="R2" t="n">
-        <v>6420244.610402202</v>
+        <v>6420236</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94594321</v>
+        <v>94594241</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718746.3058610726</v>
+        <v>718701</v>
       </c>
       <c r="R3" t="n">
-        <v>6420235.892079616</v>
+        <v>6420244</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-05-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +872,11 @@
         <v>94594243</v>
       </c>
       <c r="B4" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718785.2208272449</v>
+        <v>718785</v>
       </c>
       <c r="R4" t="n">
-        <v>6420227.356783901</v>
+        <v>6420228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2021-05-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116686235</v>
+        <v>116686229</v>
       </c>
       <c r="B5" t="n">
-        <v>97801</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +996,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1054,21 +1004,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hangvar Lilla häftings 3:1 (1) SO-hörn, Gtl</t>
+          <t>Hangvar Lilla häftings 3:1 (1) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718885</v>
+        <v>718921</v>
       </c>
       <c r="R5" t="n">
-        <v>6420135</v>
+        <v>6420209</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,6 +1048,11 @@
           <t>2024-04-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Död ved. Bild.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1114,7 +1064,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Karsthällmark.</t>
+          <t>Alvarskog med gläntor, karst.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1132,47 +1082,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116686233</v>
+        <v>116686235</v>
       </c>
       <c r="B6" t="n">
-        <v>98423</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222309</v>
+        <v>219864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,7 +1134,7 @@
         <v>718885</v>
       </c>
       <c r="R6" t="n">
-        <v>6420138</v>
+        <v>6420135</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116686231</v>
+        <v>116686216</v>
       </c>
       <c r="B7" t="n">
-        <v>98423</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,43 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hangvar Lilla häftings 3:1 (1) SO-hörn, Gtl</t>
+          <t>Hangvar Lilla häftings 3:1 (1) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718885</v>
+        <v>718907</v>
       </c>
       <c r="R7" t="n">
-        <v>6420144</v>
+        <v>6420231</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1282,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Karsthällmark.</t>
+          <t>Karstspricka.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1364,15 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116686234</v>
+        <v>116686222</v>
       </c>
       <c r="B8" t="n">
-        <v>98423</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,43 +1311,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222309</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hangvar Lilla häftings 3:1 (1) SO-hörn, Gtl</t>
+          <t>Hangvar Lilla häftings 3:1 (1) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718885</v>
+        <v>718921</v>
       </c>
       <c r="R8" t="n">
-        <v>6420135</v>
+        <v>6420209</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,6 +1373,11 @@
           <t>2024-04-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Död ved. Bild.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1462,7 +1389,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Karsthällmark.</t>
+          <t>Alvarskog med gläntor, karst.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1477,6 +1404,446 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116686240</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hangvar Lilla häftings 2:1 .NO-hörn., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>718875</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6420118</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mellanskog snitgsling av väg för skogsmaskin. Gorkänt av länsstyrelsen, röjning av buskar i Natura 2000.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Karsthällmark.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>116686231</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hangvar Lilla häftings 3:1 (1) SO-hörn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>718885</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6420144</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Karsthällmark.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>116686233</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hangvar Lilla häftings 3:1 (1) SO-hörn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>718885</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6420138</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Karsthällmark.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>116686234</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hangvar Lilla häftings 3:1 (1) SO-hörn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>718885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6420135</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Karsthällmark.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5904-2024 artfynd.xlsx
+++ b/artfynd/A 5904-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94594321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94594241</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94594243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686229</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686235</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686216</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686222</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686231</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1733,6 +1783,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686233</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,8 +1899,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>